--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -22992,7 +22992,7 @@
           <t>C | 421呎 (2房)
 $824万
 $19,580/呎
-(25年-03月)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">

--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -904,7 +761,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1000,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1230,7 +1087,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1276,7 +1133,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1179,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1368,7 +1225,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1414,7 +1271,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1460,7 +1317,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1506,7 +1363,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1782,7 +1639,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1828,7 +1685,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1874,7 +1731,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1920,7 +1777,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2012,7 +1869,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2334,7 +2191,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2380,7 +2237,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2426,7 +2283,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2518,7 +2375,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2840,7 +2697,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2886,7 +2743,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2932,7 +2789,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2978,7 +2835,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3024,7 +2881,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3254,7 +3111,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3346,7 +3203,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3392,7 +3249,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3438,7 +3295,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3530,7 +3387,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3760,7 +3617,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3852,7 +3709,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3898,7 +3755,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3944,7 +3801,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3990,7 +3847,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4036,7 +3893,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4266,7 +4123,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4312,7 +4169,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4358,7 +4215,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4404,7 +4261,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4450,7 +4307,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4496,7 +4353,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4542,7 +4399,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4772,7 +4629,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4818,7 +4675,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4864,7 +4721,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4910,7 +4767,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4956,7 +4813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5002,7 +4859,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5048,7 +4905,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5094,7 +4951,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5278,7 +5135,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5324,7 +5181,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5370,7 +5227,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5416,7 +5273,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5462,7 +5319,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5554,7 +5411,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5600,7 +5457,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5784,7 +5641,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5830,7 +5687,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5876,7 +5733,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5922,7 +5779,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5968,7 +5825,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6014,7 +5871,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6060,7 +5917,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6106,7 +5963,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6152,7 +6009,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6290,7 +6147,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6336,7 +6193,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6382,7 +6239,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6428,7 +6285,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6474,7 +6331,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6520,7 +6377,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6566,7 +6423,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6612,7 +6469,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6796,7 +6653,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6842,7 +6699,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6888,7 +6745,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6934,7 +6791,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6980,7 +6837,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7026,7 +6883,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7118,7 +6975,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7302,7 +7159,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7348,7 +7205,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7394,7 +7251,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7440,7 +7297,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7486,7 +7343,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7532,7 +7389,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7624,7 +7481,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7670,7 +7527,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7762,7 +7619,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7808,7 +7665,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7854,7 +7711,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7900,7 +7757,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7946,7 +7803,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8038,7 +7895,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8130,7 +7987,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8176,7 +8033,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8268,7 +8125,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8314,7 +8171,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8360,7 +8217,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8406,7 +8263,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8452,7 +8309,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8544,7 +8401,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8636,7 +8493,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8682,7 +8539,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8774,7 +8631,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8820,7 +8677,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8866,7 +8723,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8912,7 +8769,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8958,7 +8815,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9050,7 +8907,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9096,7 +8953,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9142,7 +8999,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9188,7 +9045,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9280,7 +9137,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9326,7 +9183,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9372,7 +9229,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9418,7 +9275,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9464,7 +9321,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9556,7 +9413,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9648,7 +9505,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9832,7 +9689,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9878,7 +9735,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9924,7 +9781,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -9970,7 +9827,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10062,7 +9919,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10154,7 +10011,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10338,7 +10195,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10430,7 +10287,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10476,7 +10333,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10568,7 +10425,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10660,7 +10517,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10844,7 +10701,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10982,7 +10839,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11074,7 +10931,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11442,7 +11299,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11488,7 +11345,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -12006,7 +11863,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12052,7 +11909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12144,7 +12001,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12378,7 +12235,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12516,7 +12373,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12608,7 +12465,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12980,7 +12837,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13026,7 +12883,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13398,7 +13255,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13444,7 +13301,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13490,7 +13347,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13582,7 +13439,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13862,7 +13719,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13908,7 +13765,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13954,7 +13811,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14000,7 +13857,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14046,7 +13903,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14326,7 +14183,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14372,7 +14229,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14418,7 +14275,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14510,7 +14367,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14794,7 +14651,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14840,7 +14697,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14886,7 +14743,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14978,7 +14835,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15254,7 +15111,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15346,7 +15203,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15438,7 +15295,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15718,7 +15575,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15764,7 +15621,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15810,7 +15667,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -16031,7 +15888,7 @@
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
@@ -16040,14 +15897,14 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
         <v>10961000</v>
       </c>
       <c r="I335" s="5" t="n">
-        <v>20720</v>
+        <v>20838</v>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
@@ -16178,7 +16035,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16224,7 +16081,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16270,7 +16127,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16362,7 +16219,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -16550,7 +16407,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16596,7 +16453,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -16642,7 +16499,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -16688,7 +16545,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16734,7 +16591,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16780,7 +16637,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -16826,7 +16683,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -17010,7 +16867,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -17056,7 +16913,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17102,7 +16959,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17148,7 +17005,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -17240,7 +17097,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17470,7 +17327,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -17516,7 +17373,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -17562,7 +17419,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -17608,7 +17465,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -17700,7 +17557,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -17746,7 +17603,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -18022,7 +17879,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -18068,7 +17925,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18114,7 +17971,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18160,7 +18017,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18390,7 +18247,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -18486,7 +18343,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -18532,7 +18389,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -18578,7 +18435,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -18624,7 +18481,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -18854,7 +18711,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -18946,7 +18803,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -18992,7 +18849,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -19084,7 +18941,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -19318,7 +19175,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -19410,7 +19267,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -19456,7 +19313,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -19548,7 +19405,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -19594,7 +19451,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -19870,7 +19727,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -19916,7 +19773,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -20380,7 +20237,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -21192,4206 +21049,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO MARE - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>235 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>232 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$962万
-$22,320/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$952万
-$22,395/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$960万
-$22,803/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,110万
-$22,607/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$948万
-$20,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 437呎 (2房)
-$910万
-$20,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 503呎 (2房)
-$1,148万
-$22,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$1,007万
-$21,790/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$895万
-$20,756/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$885万
-$20,819/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$868万
-$20,618/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,020万
-$20,774/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$828万
-$17,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$654万
-$19,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 437呎 (2房)
-$827万
-$18,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,036万
-$19,927/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$886万
-$20,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$889万
-$20,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$875万
-$18,939/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$891万
-$20,675/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$881万
-$20,736/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$865万
-$20,546/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,016万
-$20,692/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$854万
-$18,394/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$656万
-$19,629/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 437呎 (2房)
-$854万
-$19,547/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$999万
-$19,213/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$853万
-$20,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$858万
-$19,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$959万
-$20,751/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$896万
-$20,796/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$886万
-$20,859/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$861万
-$20,451/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,012万
-$20,611/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$842万
-$18,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$654万
-$19,566/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$825万
-$18,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,027万
-$19,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$850万
-$19,988/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$864万
-$20,005/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$900万
-$19,476/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$893万
-$20,712/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$883万
-$20,776/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$866万
-$20,572/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,008万
-$20,530/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$820万
-$17,681/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$668万
-$20,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$850万
-$19,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$989万
-$19,023/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$846万
-$19,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$863万
-$19,968/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$876万
-$18,972/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$889万
-$20,631/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$879万
-$20,692/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$871万
-$20,694/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,003万
-$20,436/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$846万
-$18,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$666万
-$19,943/呎
-(23年-09月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$848万
-$19,229/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$985万
-$18,948/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$872万
-$20,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$861万
-$19,928/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$896万
-$19,396/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$894万
-$20,754/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$876万
-$20,609/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$868万
-$20,610/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$1,009万
-$20,558/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$843万
-$18,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$663万
-$19,841/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$845万
-$19,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,015万
-$19,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$839万
-$19,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$859万
-$19,891/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$863万
-$18,684/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$900万
-$20,877/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$908万
-$21,358/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$863万
-$20,501/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$996万
-$20,285/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$813万
-$17,519/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$657万
-$19,668/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$815万
-$18,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 521呎 (2房)
-$1,011万
-$19,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$864万
-$20,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$849万
-$19,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$889万
-$19,245/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$885万
-$20,543/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$866万
-$20,381/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$858万
-$20,382/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$974万
-$19,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$808万
-$17,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$630万
-$18,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$838万
-$18,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,003万
-$19,285/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$829万
-$19,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$876万
-$20,282/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$853万
-$18,461/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$884万
-$20,506/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$864万
-$20,320/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$847万
-$20,121/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 491呎 (2房)
-$968万
-$19,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$824万
-$17,763/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$651万
-$19,503/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$808万
-$18,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$999万
-$19,208/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$854万
-$20,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$875万
-$20,245/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$879万
-$19,017/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$873万
-$20,262/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$861万
-$20,261/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$830万
-$19,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$934万
-$19,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$804万
-$17,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$648万
-$19,389/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$806万
-$18,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$952万
-$18,317/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$815万
-$19,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$835万
-$19,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$846万
-$18,314/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$872万
-$20,225/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$867万
-$20,402/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$835万
-$19,841/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$965万
-$19,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$829万
-$17,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$624万
-$18,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$831万
-$18,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 521呎 (2房)
-$921万
-$17,679/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$800万
-$18,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$862万
-$19,956/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$872万
-$18,866/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$870万
-$20,188/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$864万
-$20,341/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$834万
-$19,805/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$931万
-$18,998/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$806万
-$17,381/呎
-(23年-09月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$644万
-$19,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$829万
-$18,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$908万
-$17,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$822万
-$19,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$849万
-$19,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$832万
-$17,998/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$842万
-$19,538/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$845万
-$19,882/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$853万
-$20,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$961万
-$19,608/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$805万
-$17,356/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$621万
-$18,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$800万
-$18,152/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$900万
-$17,308/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$814万
-$19,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$827万
-$19,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$832万
-$18,015/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$869万
-$20,165/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$868万
-$20,421/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$852万
-$20,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$959万
-$19,569/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$804万
-$17,330/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$618万
-$18,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$826万
-$18,741/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$918万
-$17,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$786万
-$18,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$799万
-$18,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$824万
-$17,846/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$868万
-$20,128/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$865万
-$20,360/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$850万
-$20,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$926万
-$18,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$803万
-$17,304/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$633万
-$18,949/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$805万
-$18,252/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 521呎 (2房)
-$896万
-$17,190/呎
-(23年-03月)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$784万
-$18,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$824万
-$19,079/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$823万
-$17,810/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$864万
-$20,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$852万
-$20,038/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$847万
-$20,112/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$922万
-$18,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$821万
-$17,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$600万
-$17,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$802万
-$18,195/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$922万
-$17,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$781万
-$18,379/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$821万
-$19,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$820万
-$17,738/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$871万
-$20,213/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$858万
-$20,179/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$824万
-$19,580/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$941万
-$19,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$799万
-$17,224/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$619万
-$18,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$801万
-$18,172/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$919万
-$17,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$806万
-$18,969/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$792万
-$18,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$809万
-$17,509/呎
-(23年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$869万
-$20,172/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$855万
-$20,118/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$823万
-$19,539/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$950万
-$19,380/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$798万
-$17,198/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$597万
-$17,871/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$800万
-$18,141/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$917万
-$17,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$805万
-$18,934/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$818万
-$18,935/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$816万
-$17,667/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-$885万
-$20,536/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$852万
-$20,056/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 421呎 (2房)
-$821万
-$19,496/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 490呎 (2房)
-$917万
-$18,706/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$797万
-$17,172/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$595万
-$17,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$817万
-$18,526/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$885万
-$17,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$777万
-$18,275/呎
-(23年-05月)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$796万
-$18,431/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$788万
-$17,048/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 394呎 (2房)
-$887万
-$22,513/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 388呎 (2房)
-$875万
-$22,552/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 384呎 (2房)
-$885万
-$23,055/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 453呎 (2房)
-$1,034万
-$22,837/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$796万
-$17,144/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-$594万
-$17,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 441呎 (2房)
-$816万
-$18,494/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$884万
-$17,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 425呎 (2房)
-$782万
-$18,395/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 432呎 (2房)
-$795万
-$18,396/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>L | 462呎 (2房)
-$786万
-$17,015/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr"/>
-      <c r="C27" s="18" t="inlineStr"/>
-      <c r="D27" s="18" t="inlineStr"/>
-      <c r="E27" s="18" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr"/>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="18" t="inlineStr"/>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 470呎 (2房)
-$1,010万
-$21,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 388呎 (2房)
-$924万
-$23,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (2房)
-$912万
-$23,101/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>L | 423呎 (2房)
-$886万
-$20,946/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO MARE - 9座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>209 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>184 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$959万
-$22,364/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$955万
-$22,167/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$1,038万
-$22,381/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 1078呎 (3房)
-$2,480万
-$23,006/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 415呎 (2房)
-$926万
-$22,318/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$903万
-$21,042/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$902万
-$20,940/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$972万
-$20,950/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$913万
-$20,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$672万
-$21,690/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,019万
-$20,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$695万
-$21,997/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$955万
-$19,521/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 417呎 (2房)
-$841万
-$20,168/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$899万
-$20,958/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$899万
-$20,856/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$965万
-$20,797/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$910万
-$20,908/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$653万
-$21,071/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 501呎 (2房)
-$982万
-$19,591/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$670万
-$21,187/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$951万
-$19,444/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$809万
-$19,445/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$896万
-$20,876/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$904万
-$20,979/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$956万
-$20,603/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$884万
-$20,310/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$667万
-$21,519/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,011万
-$20,220/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$690万
-$21,823/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$947万
-$19,366/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$834万
-$20,041/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$892万
-$20,793/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$901万
-$20,896/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$922万
-$19,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$880万
-$20,230/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$642万
-$20,726/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$974万
-$19,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$687万
-$21,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$943万
-$19,290/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$810万
-$19,481/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$889万
-$20,730/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$898万
-$20,833/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$952万
-$20,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$869万
-$19,977/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$662万
-$21,348/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,003万
-$20,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$662万
-$20,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$940万
-$19,213/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$828万
-$19,911/呎
-(23年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$869万
-$20,249/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$904万
-$20,979/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$919万
-$19,804/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$873万
-$20,069/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$659万
-$21,265/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$966万
-$19,318/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$681万
-$21,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$936万
-$19,135/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$805万
-$19,353/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,162万
-$21,972/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$867万
-$20,205/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$902万
-$20,916/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$949万
-$20,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$870万
-$19,989/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$635万
-$20,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$962万
-$19,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$656万
-$20,769/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$796万
-$19,125/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$883万
-$20,587/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$896万
-$20,791/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$947万
-$20,409/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$863万
-$19,830/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$651万
-$21,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 501呎 (2房)
-$990万
-$19,760/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$673万
-$21,307/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$925万
-$18,908/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$797万
-$19,161/呎
-(23年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,096万
-$20,720/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$858万
-$20,009/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$893万
-$20,729/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$921万
-$19,845/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$859万
-$19,749/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$649万
-$20,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$983万
-$19,662/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$670万
-$21,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$921万
-$18,834/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$794万
-$19,099/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$876万
-$20,431/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$891万
-$20,668/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$941万
-$20,289/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$878万
-$20,172/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$625万
-$20,155/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$947万
-$18,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$668万
-$21,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$917万
-$18,759/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$792万
-$19,036/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,139万
-$21,539/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$875万
-$20,389/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$888万
-$20,606/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$938万
-$20,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$845万
-$19,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$644万
-$20,761/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$975万
-$19,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$665万
-$21,054/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$937万
-$19,157/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$783万
-$18,812/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,131万
-$21,386/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$868万
-$20,245/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$885万
-$20,543/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$913万
-$19,668/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$842万
-$19,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$619万
-$19,968/呎
-(23年-09月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$939万
-$18,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$662万
-$20,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$902万
-$18,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$778万
-$18,697/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,120万
-$21,168/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$867万
-$20,203/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$850万
-$19,722/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$902万
-$19,442/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$867万
-$19,931/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$622万
-$20,077/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$968万
-$19,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$660万
-$20,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$899万
-$18,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$786万
-$18,901/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,112万
-$21,023/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$849万
-$19,800/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$880万
-$20,420/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$907万
-$19,552/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$855万
-$19,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$600万
-$19,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$932万
-$18,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$657万
-$20,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$903万
-$18,462/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 417呎 (2房)
-$791万
-$18,969/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,109万
-$20,960/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$881万
-$20,531/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$852万
-$19,763/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$904万
-$19,491/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$827万
-$19,009/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$598万
-$19,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$919万
-$18,380/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$648万
-$20,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$788万
-$18,933/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$874万
-$20,382/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$890万
-$20,643/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$899万
-$19,375/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$812万
-$18,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$599万
-$19,316/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$916万
-$18,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$624万
-$19,763/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$884万
-$18,070/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 417呎 (2房)
-$782万
-$18,763/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,099万
-$20,773/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$873万
-$20,340/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$870万
-$20,179/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$919万
-$19,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$810万
-$18,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$597万
-$19,255/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 501呎 (2房)
-$893万
-$17,824/呎
-(23年-05月)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$622万
-$19,696/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$877万
-$17,939/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$754万
-$18,127/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$870万
-$20,268/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$884万
-$20,520/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$894万
-$19,261/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$787万
-$18,085/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$595万
-$19,190/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$870万
-$17,404/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$600万
-$18,984/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$851万
-$17,407/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$752万
-$18,067/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-$1,092万
-$20,648/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$868万
-$20,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$882万
-$20,459/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$891万
-$19,203/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-$804万
-$18,478/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 310呎 (1房)
-$593万
-$19,123/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$897万
-$17,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 316呎 (1房)
-$618万
-$19,563/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$874万
-$17,875/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 416呎 (2房)
-$756万
-$18,163/呎
-(23年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 529呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$879万
-$20,397/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 464呎 (2房)
-$888万
-$19,144/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr"/>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$606万
-$19,000/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 461呎 (2房)
-$921万
-$19,983/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 318呎 (1房)
-$601万
-$18,896/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 489呎 (2房)
-$878万
-$17,963/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 379呎 (2房)
-$859万
-$22,660/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr"/>
-      <c r="C27" s="18" t="inlineStr"/>
-      <c r="D27" s="18" t="inlineStr"/>
-      <c r="E27" s="18" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr"/>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 743呎 (3房)
-$1,398万
-$18,816/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr"/>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 725呎 (3房)
-$1,384万
-$19,090/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21049,4 +21246,4206 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$962万
+$22,320/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$952万
+$22,395/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$960万
+$22,803/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1110万
+$22,607/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$948万
+$20,422/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$910万
+$20,826/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$1148万
+$22,815/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$1007万
+$21,790/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$895万
+$20,756/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$885万
+$20,819/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$868万
+$20,618/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1020万
+$20,774/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$828万
+$17,843/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$654万
+$19,575/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$827万
+$18,918/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1036万
+$19,927/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$886万
+$20,838/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$889万
+$20,586/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$875万
+$18,939/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$891万
+$20,675/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$881万
+$20,736/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$865万
+$20,546/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1016万
+$20,692/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$854万
+$18,394/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$656万
+$19,629/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$854万
+$19,547/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$999万
+$19,213/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$853万
+$20,068/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$858万
+$19,873/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$959万
+$20,751/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$896万
+$20,796/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$886万
+$20,859/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$861万
+$20,451/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1012万
+$20,611/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$842万
+$18,136/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$654万
+$19,566/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$825万
+$18,707/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1027万
+$19,750/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$850万
+$19,988/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$864万
+$20,005/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$900万
+$19,476/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$893万
+$20,712/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$883万
+$20,776/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$866万
+$20,572/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1008万
+$20,530/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$820万
+$17,681/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$668万
+$20,000/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$850万
+$19,286/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$989万
+$19,023/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$846万
+$19,911/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$863万
+$19,968/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$876万
+$18,972/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$889万
+$20,631/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$879万
+$20,692/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$871万
+$20,694/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1003万
+$20,436/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$846万
+$18,228/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$666万
+$19,943/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$848万
+$19,229/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$985万
+$18,948/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$872万
+$20,506/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$861万
+$19,928/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$896万
+$19,396/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$894万
+$20,754/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$876万
+$20,609/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$868万
+$20,610/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$1009万
+$20,558/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$843万
+$18,172/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$663万
+$19,841/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$845万
+$19,168/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1015万
+$19,515/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$839万
+$19,751/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$859万
+$19,891/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$863万
+$18,684/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$900万
+$20,877/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$908万
+$21,358/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$863万
+$20,501/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$996万
+$20,285/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$813万
+$17,519/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$657万
+$19,668/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$815万
+$18,481/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 521呎 (2房)
+$1011万
+$19,401/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$864万
+$20,341/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$849万
+$19,650/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$889万
+$19,245/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$885万
+$20,543/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$866万
+$20,381/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$858万
+$20,382/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$974万
+$19,880/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$808万
+$17,414/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$630万
+$18,865/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$838万
+$18,995/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1003万
+$19,285/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$829万
+$19,515/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$876万
+$20,282/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$853万
+$18,461/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$884万
+$20,506/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$864万
+$20,320/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$847万
+$20,121/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 491呎 (2房)
+$968万
+$19,719/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$824万
+$17,763/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$651万
+$19,503/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$808万
+$18,322/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$999万
+$19,208/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$854万
+$20,101/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$875万
+$20,245/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$879万
+$19,017/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$873万
+$20,262/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$861万
+$20,261/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$830万
+$19,710/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$934万
+$19,071/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$804万
+$17,323/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$648万
+$19,389/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$806万
+$18,277/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$952万
+$18,317/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$815万
+$19,172/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$835万
+$19,336/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$846万
+$18,314/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$872万
+$20,225/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$867万
+$20,402/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$835万
+$19,841/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$965万
+$19,686/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$829万
+$17,869/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$624万
+$18,695/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$831万
+$18,848/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 521呎 (2房)
+$921万
+$17,679/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$800万
+$18,824/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$862万
+$19,956/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$872万
+$18,866/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$870万
+$20,188/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$864万
+$20,341/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$834万
+$19,805/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$931万
+$18,998/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$806万
+$17,381/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$644万
+$19,272/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$829万
+$18,803/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$908万
+$17,471/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$822万
+$19,344/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$849万
+$19,650/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$832万
+$17,998/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$842万
+$19,538/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$845万
+$19,882/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$853万
+$20,266/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$961万
+$19,608/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$805万
+$17,356/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$621万
+$18,581/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$800万
+$18,152/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$900万
+$17,308/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$814万
+$19,153/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$827万
+$19,148/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$832万
+$18,015/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$869万
+$20,165/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$868万
+$20,421/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$852万
+$20,226/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$959万
+$19,569/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$804万
+$17,330/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$618万
+$18,488/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$826万
+$18,741/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$918万
+$17,658/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$786万
+$18,485/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$799万
+$18,486/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$824万
+$17,846/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$868万
+$20,128/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$865万
+$20,360/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$850万
+$20,190/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$926万
+$18,888/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$803万
+$17,304/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$633万
+$18,949/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$805万
+$18,252/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 521呎 (2房)
+$896万
+$17,190/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$784万
+$18,452/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$824万
+$19,079/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$823万
+$17,810/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$864万
+$20,049/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$852万
+$20,038/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$847万
+$20,112/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$922万
+$18,814/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$821万
+$17,690/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$600万
+$17,964/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$802万
+$18,195/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$922万
+$17,723/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$781万
+$18,379/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$821万
+$19,007/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$820万
+$17,738/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$871万
+$20,213/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$858万
+$20,179/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$824万
+$19,580/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$941万
+$19,206/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$799万
+$17,224/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$619万
+$18,527/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$801万
+$18,172/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$919万
+$17,679/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$806万
+$18,969/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$792万
+$18,345/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$809万
+$17,509/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$869万
+$20,172/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$855万
+$20,118/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$823万
+$19,539/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$950万
+$19,380/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$798万
+$17,198/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$597万
+$17,871/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$800万
+$18,141/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$917万
+$17,637/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$805万
+$18,934/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$818万
+$18,935/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$816万
+$17,667/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+$885万
+$20,536/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$852万
+$20,056/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 421呎 (2房)
+$821万
+$19,496/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 490呎 (2房)
+$917万
+$18,706/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$797万
+$17,172/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$595万
+$17,823/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$817万
+$18,526/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$885万
+$17,012/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$777万
+$18,275/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$796万
+$18,431/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$788万
+$17,048/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 394呎 (2房)
+$887万
+$22,513/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 388呎 (2房)
+$875万
+$22,552/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 384呎 (2房)
+$885万
+$23,055/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 453呎 (2房)
+$1034万
+$22,837/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$796万
+$17,144/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+$594万
+$17,775/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 441呎 (2房)
+$816万
+$18,494/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$884万
+$17,000/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 425呎 (2房)
+$782万
+$18,395/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 432呎 (2房)
+$795万
+$18,396/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>L | 462呎 (2房)
+$786万
+$17,015/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr"/>
+      <c r="C26" s="22" t="inlineStr"/>
+      <c r="D26" s="22" t="inlineStr"/>
+      <c r="E26" s="22" t="inlineStr"/>
+      <c r="F26" s="22" t="inlineStr"/>
+      <c r="G26" s="22" t="inlineStr"/>
+      <c r="H26" s="22" t="inlineStr"/>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 470呎 (2房)
+$1010万
+$21,481/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 388呎 (2房)
+$924万
+$23,822/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (2房)
+$912万
+$23,101/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>L | 423呎 (2房)
+$886万
+$20,946/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>9座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$959万
+$22,364/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$955万
+$22,167/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$1038万
+$22,381/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 1078呎 (3房)
+$2480万
+$23,006/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 415呎 (2房)
+$926万
+$22,318/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$903万
+$21,042/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$902万
+$20,940/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$972万
+$20,950/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$913万
+$20,991/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$672万
+$21,690/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1019万
+$20,382/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$695万
+$21,997/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$955万
+$19,521/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 417呎 (2房)
+$841万
+$20,168/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$899万
+$20,958/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$899万
+$20,856/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$965万
+$20,797/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$910万
+$20,908/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$653万
+$21,071/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 501呎 (2房)
+$982万
+$19,591/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$670万
+$21,187/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$951万
+$19,444/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$809万
+$19,445/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$896万
+$20,876/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$904万
+$20,979/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$956万
+$20,603/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$884万
+$20,310/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$667万
+$21,519/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1011万
+$20,220/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$690万
+$21,823/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$947万
+$19,366/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$834万
+$20,041/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$892万
+$20,793/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$901万
+$20,896/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$922万
+$19,866/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$880万
+$20,230/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$642万
+$20,726/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$974万
+$19,474/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$687万
+$21,734/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$943万
+$19,290/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$810万
+$19,481/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$889万
+$20,730/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$898万
+$20,833/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$952万
+$20,513/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$869万
+$19,977/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$662万
+$21,348/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1003万
+$20,058/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$662万
+$20,934/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$940万
+$19,213/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$828万
+$19,911/呎
+(23年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$869万
+$20,249/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$904万
+$20,979/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$919万
+$19,804/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$873万
+$20,069/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$659万
+$21,265/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$966万
+$19,318/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$681万
+$21,563/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$936万
+$19,135/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$805万
+$19,353/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1162万
+$21,972/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$867万
+$20,205/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$902万
+$20,916/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$949万
+$20,446/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$870万
+$19,989/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$635万
+$20,481/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$962万
+$19,244/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$656万
+$20,769/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$796万
+$19,125/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$883万
+$20,587/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$896万
+$20,791/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$947万
+$20,409/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$863万
+$19,830/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$651万
+$21,010/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 501呎 (2房)
+$990万
+$19,760/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$673万
+$21,307/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$925万
+$18,908/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$797万
+$19,161/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 526呎 (2房)
+$1096万
+$20,838/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$858万
+$20,009/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$893万
+$20,729/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$921万
+$19,845/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$859万
+$19,749/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$649万
+$20,929/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$983万
+$19,662/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$670万
+$21,218/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$921万
+$18,834/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$794万
+$19,099/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$876万
+$20,431/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$891万
+$20,668/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$941万
+$20,289/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$878万
+$20,172/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$625万
+$20,155/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$947万
+$18,938/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$668万
+$21,136/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$917万
+$18,759/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$792万
+$19,036/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1139万
+$21,539/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$875万
+$20,389/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$888万
+$20,606/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$938万
+$20,226/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$845万
+$19,428/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$644万
+$20,761/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$975万
+$19,506/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$665万
+$21,054/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$937万
+$19,157/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$783万
+$18,812/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1131万
+$21,386/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$868万
+$20,245/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$885万
+$20,543/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$913万
+$19,668/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$842万
+$19,352/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$619万
+$19,968/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$939万
+$18,788/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$662万
+$20,965/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$902万
+$18,452/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$778万
+$18,697/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1120万
+$21,168/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$867万
+$20,203/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$850万
+$19,722/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$902万
+$19,442/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$867万
+$19,931/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$622万
+$20,077/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$968万
+$19,350/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$660万
+$20,883/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$899万
+$18,378/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$786万
+$18,901/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1112万
+$21,023/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$849万
+$19,800/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$880万
+$20,420/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$907万
+$19,552/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$855万
+$19,655/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$600万
+$19,352/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$932万
+$18,638/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$657万
+$20,801/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$903万
+$18,462/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 417呎 (2房)
+$791万
+$18,969/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1109万
+$20,960/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$881万
+$20,531/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$852万
+$19,763/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$904万
+$19,491/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$827万
+$19,009/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$598万
+$19,284/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$919万
+$18,380/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$648万
+$20,513/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$788万
+$18,933/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$874万
+$20,382/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$890万
+$20,643/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$899万
+$19,375/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$812万
+$18,674/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$599万
+$19,316/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$916万
+$18,312/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$624万
+$19,763/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$884万
+$18,070/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 417呎 (2房)
+$782万
+$18,763/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1099万
+$20,773/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$873万
+$20,340/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$870万
+$20,179/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$919万
+$19,808/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$810万
+$18,609/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$597万
+$19,255/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 501呎 (2房)
+$893万
+$17,824/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$622万
+$19,696/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$877万
+$17,939/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$754万
+$18,127/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$870万
+$20,268/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$884万
+$20,520/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$894万
+$19,261/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$787万
+$18,085/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$595万
+$19,190/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$870万
+$17,404/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$600万
+$18,984/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$851万
+$17,407/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$752万
+$18,067/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+$1092万
+$20,648/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$868万
+$20,231/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$882万
+$20,459/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$891万
+$19,203/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+$804万
+$18,478/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 310呎 (1房)
+$593万
+$19,123/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$897万
+$17,938/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 316呎 (1房)
+$618万
+$19,563/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$874万
+$17,875/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 416呎 (2房)
+$756万
+$18,163/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 529呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$879万
+$20,397/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 464呎 (2房)
+$888万
+$19,144/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$606万
+$19,000/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 461呎 (2房)
+$921万
+$19,983/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 318呎 (1房)
+$601万
+$18,896/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 489呎 (2房)
+$878万
+$17,963/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 379呎 (2房)
+$859万
+$22,660/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr"/>
+      <c r="C26" s="22" t="inlineStr"/>
+      <c r="D26" s="22" t="inlineStr"/>
+      <c r="E26" s="22" t="inlineStr"/>
+      <c r="F26" s="22" t="inlineStr"/>
+      <c r="G26" s="22" t="inlineStr"/>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 743呎 (3房)
+$1398万
+$18,816/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr"/>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 725呎 (3房)
+$1384万
+$19,090/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO MARE.xlsx
@@ -671,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
